--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1343,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="17" min="2" max="2"/>
@@ -1370,6 +1370,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="17">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -1455,7 +1456,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>syrnyky:8,borscht:1,chicken:6</t>
+          <t>syrnyky:8,borscht:1,zrazy:6,chicken:8</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -1466,7 +1467,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>assets/IMG_1259.JPG</t>
+          <t>assets/hf_20260308_101724_332ed7b633c04af6be57da9339c4624d.jpeg</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1504,7 +1505,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>syrnyky:8,solyanka:1,chicken:6</t>
+          <t>syrnyky:8,solyanka:1,zrazy:6,chicken:8</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
@@ -1515,7 +1516,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>assets/IMG_1259.JPG</t>
+          <t>assets/hf_20260308_101754_0817f1096b73448d87eb3531e411155b.png</t>
         </is>
       </c>
       <c r="K6" s="3" t="n"/>
@@ -1553,7 +1554,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>syrnyky:16,borscht:2,chicken:16</t>
+          <t>syrnyky:16,borscht:2,zrazy:12,chicken:16</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -1606,7 +1607,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>syrnyky:8,shakshuka:2,solyanka:2,chicken:16</t>
+          <t>syrnyky:8,shakshuka:2,solyanka:2,zrazy:12,chicken:16</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
@@ -1617,7 +1618,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102232_0b1e6e0deade4ce2934cc28ee2635165.png</t>
+          <t>assets/hf_20260308_102519_c328da66a77a47afaa22022eb4f842f1.png</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -1655,7 +1656,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>syrnyky:16,borscht:2,solyanka:1,chicken:20</t>
+          <t>syrnyky:24,borscht:2,solyanka:1,zrazy:16,chicken:20</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -1704,7 +1705,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>syrnyky:16,shakshuka:2,borscht:1,solyanka:2,chicken:20</t>
+          <t>syrnyky:16,shakshuka:2,borscht:1,solyanka:2,zrazy:16,chicken:20</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
@@ -1715,7 +1716,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102551_7e65581e179545a7a46d6504b44e7e7b.png</t>
+          <t>assets/hf_20260308_103416_d2ba00b8715544dfb6886f8a1950d1c6.jpeg</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
@@ -1967,7 +1968,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>assets/nobg/syrnyky.png</t>
+          <t>assets/products/syrnyky.png</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1990,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>assets/nobg/chicken.png</t>
+          <t>assets/products/chicken.png</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2012,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>assets/nobg/borscht.png</t>
+          <t>assets/products/borscht.png</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2034,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>assets/nobg/solyanka.png</t>
+          <t>assets/products/solyanka.png</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2056,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>assets/nobg/shakshuka.png</t>
+          <t>assets/products/shakshuka.png</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2078,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>assets/nobg/zrazy.png</t>
+          <t>assets/products/zrazy.png</t>
         </is>
       </c>
     </row>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101724_332ed7b633c04af6be57da9339c4624d.jpeg</t>
+          <t>assets/hf_20260308_101724_332ed7b6-33c0-4af6-be57-da9339c4624d.jpeg</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101754_0817f1096b73448d87eb3531e411155b.png</t>
+          <t>assets/hf_20260308_101754_0817f109-6b73-448d-87eb-3531e411155b.png</t>
         </is>
       </c>
       <c r="K6" s="3" t="n"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102232_0b1e6e0deade4ce2934cc28ee2635165.png</t>
+          <t>assets/hf_20260308_102232_0b1e6e0d-eade-4ce2-934c-c28ee2635165.png</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102519_c328da66a77a47afaa22022eb4f842f1.png</t>
+          <t>assets/hf_20260308_102519_c328da66-a77a-47af-aa22-022eb4f842f1.png</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102551_7e65581e179545a7a46d6504b44e7e7b.png</t>
+          <t>assets/hf_20260308_102551_7e65581e-1795-45a7-a46d-6504b44e7e7b.png</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_103416_d2ba00b8715544dfb6886f8a1950d1c6.jpeg</t>
+          <t>assets/hf_20260308_103416_d2ba00b8-7155-44df-b688-6f8a1950d1c6.jpeg</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101724_332ed7b633c04af6be57da9339c4624d.jpeg</t>
+          <t>assets/hf_20260308_101724_332ed7b6-33c0-4af6-be57-da9339c4624d.jpeg</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101754_0817f1096b73448d87eb3531e411155b.png</t>
+          <t>assets/hf_20260308_101754_0817f109-6b73-448d-87eb-3531e411155b.png</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102232_0b1e6e0deade4ce2934cc28ee2635165.png</t>
+          <t>assets/hf_20260308_102232_0b1e6e0d-eade-4ce2-934c-c28ee2635165.png</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102519_c328da66a77a47afaa22022eb4f842f1.png</t>
+          <t>assets/hf_20260308_102519_c328da66-a77a-47af-aa22-022eb4f842f1.png</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102551_7e65581e179545a7a46d6504b44e7e7b.png</t>
+          <t>assets/hf_20260308_102551_7e65581e-1795-45a7-a46d-6504b44e7e7b.png</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_103416_d2ba00b8715544dfb6886f8a1950d1c6.jpeg</t>
+          <t>assets/hf_20260308_103416_d2ba00b8-7155-44df-b688-6f8a1950d1c6.jpeg</t>
         </is>
       </c>
     </row>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -181,6 +181,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -555,30 +556,30 @@
   <dimension ref="B1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" style="17" min="2" max="2"/>
-    <col width="18" customWidth="1" style="17" min="3" max="5"/>
-    <col width="12" customWidth="1" style="17" min="6" max="6"/>
-    <col width="40" customWidth="1" style="17" min="7" max="9"/>
-    <col width="10" customWidth="1" style="17" min="10" max="12"/>
-    <col width="22" customWidth="1" style="17" min="13" max="14"/>
-    <col width="8" customWidth="1" style="17" min="15" max="15"/>
+    <col width="4" customWidth="1" style="18" min="2" max="2"/>
+    <col width="18" customWidth="1" style="18" min="3" max="5"/>
+    <col width="12" customWidth="1" style="18" min="6" max="6"/>
+    <col width="40" customWidth="1" style="18" min="7" max="9"/>
+    <col width="10" customWidth="1" style="18" min="10" max="12"/>
+    <col width="22" customWidth="1" style="18" min="13" max="14"/>
+    <col width="8" customWidth="1" style="18" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" s="17">
-      <c r="B1" s="16" t="inlineStr">
+    <row r="1" ht="17.4" customHeight="1" s="18">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>🛒  HUTKO Kitchen — Product Catalogue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Edit this sheet to update the shop. photo_file = filename in assets/ folder. dietary = comma-separated tags.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="17">
+    <row r="4" ht="30" customHeight="1" s="18">
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -650,7 +651,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40.05" customHeight="1" s="17">
+    <row r="5" ht="40.05" customHeight="1" s="18">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>syrnyky</t>
@@ -716,7 +717,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40.05" customHeight="1" s="17">
+    <row r="6" ht="40.05" customHeight="1" s="18">
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>chicken</t>
@@ -786,7 +787,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="40.05" customHeight="1" s="17">
+    <row r="7" ht="40.05" customHeight="1" s="18">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>borscht</t>
@@ -852,7 +853,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="40.05" customHeight="1" s="17">
+    <row r="8" ht="40.05" customHeight="1" s="18">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>solyanka</t>
@@ -918,7 +919,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="40.05" customHeight="1" s="17">
+    <row r="9" ht="40.05" customHeight="1" s="18">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>shakshuka</t>
@@ -988,7 +989,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.05" customHeight="1" s="17">
+    <row r="10" ht="40.05" customHeight="1" s="18">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>zrazy</t>
@@ -1055,13 +1056,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>📦  PRODUCT VARIANTS (sizes &amp; prices)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52.8" customHeight="1" s="17">
+    <row r="13" ht="52.8" customHeight="1" s="18">
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>product_id</t>
@@ -1328,7 +1329,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1346,32 +1347,32 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" style="17" min="2" max="2"/>
-    <col width="20" customWidth="1" style="17" min="3" max="5"/>
-    <col width="10" customWidth="1" style="17" min="6" max="6"/>
-    <col width="45" customWidth="1" style="17" min="7" max="7"/>
-    <col width="12" customWidth="1" style="17" min="8" max="9"/>
-    <col width="25" customWidth="1" style="17" min="10" max="10"/>
-    <col width="15" customWidth="1" style="17" min="11" max="11"/>
-    <col width="8" customWidth="1" style="17" min="12" max="12"/>
+    <col width="4" customWidth="1" style="18" min="2" max="2"/>
+    <col width="20" customWidth="1" style="18" min="3" max="5"/>
+    <col width="10" customWidth="1" style="18" min="6" max="6"/>
+    <col width="45" customWidth="1" style="18" min="7" max="7"/>
+    <col width="12" customWidth="1" style="18" min="8" max="9"/>
+    <col width="25" customWidth="1" style="18" min="10" max="10"/>
+    <col width="15" customWidth="1" style="18" min="11" max="11"/>
+    <col width="8" customWidth="1" style="18" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" s="17">
-      <c r="B1" s="16" t="inlineStr">
+    <row r="1" ht="17.4" customHeight="1" s="18">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>🎁  HUTKO Kitchen — Bundles &amp; Packs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>items = product_id:qty,product_id:qty format. discount_price overrides calculated price.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="30" customHeight="1" s="17">
+    <row r="4" ht="30" customHeight="1" s="18">
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -1428,7 +1429,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="17">
+    <row r="5" ht="45" customHeight="1" s="18">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>pack-s1</t>
@@ -1467,7 +1468,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101724_332ed7b633c04af6be57da9339c4624d.jpeg</t>
+          <t>assets/IMG_4178.JPEG</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1477,7 +1478,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="17">
+    <row r="6" ht="45" customHeight="1" s="18">
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>pack-s2</t>
@@ -1516,7 +1517,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101754_0817f1096b73448d87eb3531e411155b.png</t>
+          <t>assets/IMG_4176.JPEG</t>
         </is>
       </c>
       <c r="K6" s="3" t="n"/>
@@ -1526,7 +1527,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="17">
+    <row r="7" ht="45" customHeight="1" s="18">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>pack-m1</t>
@@ -1565,7 +1566,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102232_0b1e6e0deade4ce2934cc28ee2635165.png</t>
+          <t>assets/IMG_4180.JPEG</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1579,7 +1580,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" s="17">
+    <row r="8" ht="45" customHeight="1" s="18">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>pack-m2</t>
@@ -1618,7 +1619,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102519_c328da66a77a47afaa22022eb4f842f1.png</t>
+          <t>assets/IMG_4180.JPEG</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -1628,7 +1629,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1" s="17">
+    <row r="9" ht="45" customHeight="1" s="18">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>pack-l1</t>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102551_7e65581e179545a7a46d6504b44e7e7b.png</t>
+          <t>assets/IMG_4156.PNG</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1677,7 +1678,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" s="17">
+    <row r="10" ht="45" customHeight="1" s="18">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>pack-l2</t>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_103416_d2ba00b8715544dfb6886f8a1950d1c6.jpeg</t>
+          <t>assets/IMG_4156.PNG</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
@@ -1734,7 +1735,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1752,12 +1753,12 @@
   <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="75" customWidth="1" style="17" min="1" max="1"/>
-    <col width="25" customWidth="1" style="17" min="2" max="2"/>
-    <col width="60" customWidth="1" style="17" min="3" max="3"/>
+    <col width="75" customWidth="1" style="18" min="1" max="1"/>
+    <col width="25" customWidth="1" style="18" min="2" max="2"/>
+    <col width="60" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="17">
+    <row r="1" ht="15.6" customHeight="1" s="18">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>📖  HOW TO USE THIS FILE</t>
@@ -1856,7 +1857,7 @@
     <row r="17">
       <c r="A17" s="8" t="n"/>
     </row>
-    <row r="18" ht="15.6" customHeight="1" s="17">
+    <row r="18" ht="15.6" customHeight="1" s="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>⚠️  AFTER EDITING:</t>
@@ -1888,7 +1889,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1907,27 +1908,27 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" style="17" min="1" max="1"/>
-    <col width="16" customWidth="1" style="17" min="2" max="2"/>
-    <col width="24" customWidth="1" style="17" min="3" max="3"/>
-    <col width="55" customWidth="1" style="17" min="4" max="4"/>
+    <col width="12" customWidth="1" style="18" min="1" max="1"/>
+    <col width="16" customWidth="1" style="18" min="2" max="2"/>
+    <col width="24" customWidth="1" style="18" min="3" max="3"/>
+    <col width="55" customWidth="1" style="18" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="17">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="18">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>🖼️  HUTKO Kitchen — Image Manager</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Change photo_file values below to update images on the website. Use relative paths from the frontend folder (e.g. assets/products/syrnyky.png).</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="6" customHeight="1" s="17"/>
+    <row r="3" ht="6" customHeight="1" s="18"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2223,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2241,26 +2242,26 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="22" customWidth="1" style="17" min="1" max="1"/>
-    <col width="38" customWidth="1" style="17" min="2" max="2"/>
-    <col width="45" customWidth="1" style="17" min="3" max="3"/>
+    <col width="22" customWidth="1" style="18" min="1" max="1"/>
+    <col width="38" customWidth="1" style="18" min="2" max="2"/>
+    <col width="45" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="17">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="18">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>⚙️  HUTKO Kitchen — Contact &amp; Business Settings</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Edit values in column B. These are read by the website for the contact page, footer, and delivery info.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="6" customHeight="1" s="17"/>
+    <row r="3" ht="6" customHeight="1" s="18"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2529,7 +2530,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/IMG_4180.JPEG</t>
+          <t>assets/IMG_4156.PNG</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>assets/IMG_4156.PNG</t>
+          <t>assets/IMG_4176.JPEG</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>assets/IMG_4156.PNG</t>
+          <t>assets/IMG_4180.JPEG</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1468,7 +1468,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>assets/IMG_4178.JPEG</t>
+          <t>assets/hf_20260308_101724_332ed7b633c04af6be57da9339c4624d.jpeg</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>assets/IMG_4176.JPEG</t>
+          <t>assets/hf_20260308_101754_0817f1096b73448d87eb3531e411155b.png</t>
         </is>
       </c>
       <c r="K6" s="3" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>assets/IMG_4180.JPEG</t>
+          <t>assets/hf_20260308_102232_0b1e6e0deade4ce2934cc28ee2635165.png</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/IMG_4156.PNG</t>
+          <t>assets/hf_20260308_102519_c328da66a77a47afaa22022eb4f842f1.png</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>assets/IMG_4176.JPEG</t>
+          <t>assets/hf_20260308_102551_7e65581e179545a7a46d6504b44e7e7b.png</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>assets/IMG_4180.JPEG</t>
+          <t>assets/hf_20260308_103416_d2ba00b8715544dfb6886f8a1950d1c6.jpeg</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1468,7 +1468,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101724_332ed7b633c04af6be57da9339c4624d.jpeg</t>
+          <t>assets/IMG_4178.JPEG</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_101754_0817f1096b73448d87eb3531e411155b.png</t>
+          <t>assets/IMG_4176.JPEG</t>
         </is>
       </c>
       <c r="K6" s="3" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102232_0b1e6e0deade4ce2934cc28ee2635165.png</t>
+          <t>assets/IMG_4180.JPEG</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102519_c328da66a77a47afaa22022eb4f842f1.png</t>
+          <t>assets/IMG_4156.PNG</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_102551_7e65581e179545a7a46d6504b44e7e7b.png</t>
+          <t>assets/IMG_4180.JPEG</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>assets/hf_20260308_103416_d2ba00b8715544dfb6886f8a1950d1c6.jpeg</t>
+          <t>assets/IMG_4156.PNG</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2124" yWindow="432" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="2" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,14 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,8 +109,12 @@
       <color rgb="FF555555"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -137,6 +141,36 @@
         <fgColor rgb="FF0F6E56"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A7A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002a9d5c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B3FCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00555555"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E84B22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -150,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -181,16 +215,36 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -553,33 +607,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AE24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="4" customWidth="1" style="18" min="2" max="2"/>
-    <col width="18" customWidth="1" style="18" min="3" max="5"/>
-    <col width="12" customWidth="1" style="18" min="6" max="6"/>
-    <col width="40" customWidth="1" style="18" min="7" max="9"/>
-    <col width="10" customWidth="1" style="18" min="10" max="12"/>
-    <col width="22" customWidth="1" style="18" min="13" max="14"/>
-    <col width="8" customWidth="1" style="18" min="15" max="15"/>
+    <col width="4" customWidth="1" style="17" min="2" max="2"/>
+    <col width="18" customWidth="1" style="17" min="3" max="5"/>
+    <col width="12" customWidth="1" style="17" min="6" max="6"/>
+    <col width="40" customWidth="1" style="17" min="7" max="9"/>
+    <col width="10" customWidth="1" style="17" min="10" max="12"/>
+    <col width="24.5703125" customWidth="1" style="17" min="13" max="13"/>
+    <col width="29" customWidth="1" style="17" min="14" max="14"/>
+    <col width="8" customWidth="1" style="17" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" s="18">
-      <c r="B1" s="17" t="inlineStr">
+    <row r="1" ht="17.45" customHeight="1" s="17">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>🛒  HUTKO Kitchen — Product Catalogue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Edit this sheet to update the shop. photo_file = filename in assets/ folder. dietary = comma-separated tags.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="18">
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1" s="17">
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -640,18 +696,98 @@
           <t>photo_file</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="N4" s="22" t="inlineStr">
+        <is>
+          <t>ingredients_en</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t>dietary</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40.05" customHeight="1" s="18">
+      <c r="Q4" s="24" t="inlineStr">
+        <is>
+          <t>ingredients_ua</t>
+        </is>
+      </c>
+      <c r="R4" s="24" t="inlineStr">
+        <is>
+          <t>ingredients_nl</t>
+        </is>
+      </c>
+      <c r="S4" s="25" t="inlineStr">
+        <is>
+          <t>about_en</t>
+        </is>
+      </c>
+      <c r="T4" s="25" t="inlineStr">
+        <is>
+          <t>about_ua</t>
+        </is>
+      </c>
+      <c r="U4" s="25" t="inlineStr">
+        <is>
+          <t>about_nl</t>
+        </is>
+      </c>
+      <c r="V4" s="26" t="inlineStr">
+        <is>
+          <t>prepare_en</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="inlineStr">
+        <is>
+          <t>prepare_ua</t>
+        </is>
+      </c>
+      <c r="X4" s="26" t="inlineStr">
+        <is>
+          <t>prepare_nl</t>
+        </is>
+      </c>
+      <c r="Y4" s="27" t="inlineStr">
+        <is>
+          <t>hutko_tip_en</t>
+        </is>
+      </c>
+      <c r="Z4" s="27" t="inlineStr">
+        <is>
+          <t>hutko_tip_ua</t>
+        </is>
+      </c>
+      <c r="AA4" s="27" t="inlineStr">
+        <is>
+          <t>hutko_tip_nl</t>
+        </is>
+      </c>
+      <c r="AB4" s="28" t="inlineStr">
+        <is>
+          <t>storage_en</t>
+        </is>
+      </c>
+      <c r="AC4" s="28" t="inlineStr">
+        <is>
+          <t>storage_ua</t>
+        </is>
+      </c>
+      <c r="AD4" s="28" t="inlineStr">
+        <is>
+          <t>storage_nl</t>
+        </is>
+      </c>
+      <c r="AE4" s="28" t="inlineStr">
+        <is>
+          <t>gallery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="61.5" customHeight="1" s="17">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>syrnyky</t>
@@ -679,17 +815,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Ukrainian cottage cheese pancakes with sauces. Your calm breakfast — warm, real, no fuss.</t>
+          <t>Light and tender cottage cheese pancakes made from real cottage cheese with minimal flour. High in protein, egg-free, and perfect anytime — from breakfast to late-night cravings.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Українські сирники з соусами. Твій спокійний сніданок — теплий, справжній, без метушні.</t>
+          <t>Наші улюблені ніжні та повітряні сирники, приготовані з натурального сиру з мінімальною кількістю борошна. Багаті на білок, без яєць — ідеальні у будь-який момент: від сніданку до пізніх перекусів.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Oekraïense kwark pannenkoekjes met sauzen. Jouw rustig ontbijt — warm, echt, geen gedoe.</t>
+          <t>Onze favoriete zachte en luchtige cottage cheese pancakes, gemaakt van echte kwark met een minimale hoeveelheid bloem. Rijk aan eiwitten, zonder ei — perfect op elk moment van de dag: van ontbijt tot een late snack</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -700,7 +836,11 @@
           <t>8 pcs</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Popular</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>assets/products/syrnyky.png</t>
@@ -708,16 +848,67 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>Ingredients: Cottage cheese (milk) (76%), wheat flour (gluten), vanilla sugar (sugar, ethyl vanillin).
+Allergens: Contains milk, wheat (gluten).</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>vegetarian,gluten-free option</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.05" customHeight="1" s="18">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Take syrnyky straight from the freezer — no thawing needed. | Fry in regular oil on medium heat, 4–5 min per side until golden. | Serve with sour cream, jam, honey, or berries.</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Дістаньте сирники прямо з морозилки — розморожувати не потрібно. | Смажити на звичайній олії на середньому вогні, 4–5 хвилин з кожного боку до золотистої скоринки. | Подавати зі сметаною, джемом, медом, а також з ягодами.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Haal de syrnyky direct uit de vriezer — niet ontdooien. | Bak in gewone olie op middelhoog vuur, 4–5 min per kant tot goudbruin. | Serveer met zure room, jam, honing of bessen.</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>HUTKO tip: Try syrnyky with bacon — the mix of salty and sweet is surprisingly brilliant.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Рекомендація від HUTKO: Рекомендуємо спробувати сирники з беконом — мікс солоного та солодкого смаку дуже класно поєднується.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>HUTKO tip: Probeer syrnyky met spek — de combinatie van zout en zoet is verrassend lekker.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86.25" customHeight="1" s="17">
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>chicken</t>
@@ -730,7 +921,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Курячі кульки</t>
+          <t>Котлетки по-киівськи</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -745,17 +936,17 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Crispy outside, herb butter inside. Perfect for guests or a film evening.</t>
+          <t>Crispy and juicy mini Chicken Kyiv, made from natural chicken meat with a rich filling of butter, hard cheese, and fresh herbs (dill &amp; parsley). A classic recipe in a bite-sized format — inspired by Dutch bitterballen, but even better. Perfect anytime: from lunch to late-night cravings.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Хрустка зовні, трав'яне масло всередині. Ідеально для гостей або вечора з фільмом.</t>
+          <t>Хрусткі та соковиті міні котлети по-київськи з натурального курячого м’яса з ніжною начинкою з масла, твердого сиру та свіжої зелені (кріп і петрушка). Класика у зручному міні-форматі — натхненна голландськими bitterballen, але ще смачніша. Ідеальні у будь-який момент: від обіду до пізніх перекусів.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Knapperig van buiten, kruidenboter van binnen. Perfect voor gasten of een filmavond.</t>
+          <t>Krokante en sappige mini Chicken Kyiv, gemaakt van natuurlijk kippenvlees met een romige vulling van boter, harde kaas en verse kruiden (dille &amp; peterselie). Een klassiek gerecht in een handig bite-size formaat — geïnspireerd op Nederlandse bitterballen, maar nóg lekkerder. Perfect op elk moment: van lunch tot een late snack.</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
@@ -778,7 +969,8 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>halal option</t>
+          <t>Ingredients: Chicken fillet (50%), chicken thighs (15%), butter (milk) (11%), breadcrumbs (wheat, egg), mozzarella (milk), herbs (dill, parsley).
+Allergens: Contains milk, egg, wheat (gluten).</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -786,8 +978,43 @@
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="40.05" customHeight="1" s="18">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>halal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Take chicken balls straight from the freezer. | Heat pan with oil on medium-high, or preheat air fryer to 180°C. | Pan: fry 8–10 min, turning occasionally. Air fryer: 12 min. | Serve immediately while crispy and hot.</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Дістаньте кульки прямо з морозилки. | Розігрійте олію на сковорідці на середньо-сильному вогні або розігрійте аерофритюрницю до 180°C. | На сковорідці: смажте 8–10 хв, перевертаючи. Аерофритюрниця: 12 хв. | Подавайте одразу, поки хрусткі та гарячі.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Haal de kippenballen direct uit de vriezer. | Verhit olie in een pan op middelhoog vuur, of verwarm de airfryer voor op 180°C. | Pan: bak 8–10 min terwijl je regelmatig omdraait. Airfryer: 12 min. | Serveer direct terwijl ze knapperig en heet zijn.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66.75" customHeight="1" s="17">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>borscht</t>
@@ -805,7 +1032,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Borsjt</t>
+          <t>Borcht</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -815,17 +1042,18 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Classic Ukrainian beetroot soup, slow-cooked and rich. Just heat — 8 min on the stove.</t>
+          <t>Classic Ukrainian borscht made with beetroot, vegetables, and tender chicken meat. A rich, comforting soup full of deep flavor — perfect for lunch or dinner when you’re craving something warm and satisfying.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Класичний український буряковий суп, повільно варений і насичений. Просто нагрій — 8 хв.</t>
+          <t>Класичний український борщ на курячому бульйоні з ніжним курячим м’ясом. Насичений смак буряка та овочів — справжній смак дому в кожній ложці. Ідеальний, коли хочеться чогось теплого і рідного.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Klassieke Oekraïense bietensoep, langzaam gegaard. Gewoon opwarmen — 8 min op het fornuis.</t>
+          <t xml:space="preserve">Klassieke Oekraïense borsjtsj gemaakt met rode biet, groenten en mals kippenvlees. Een rijke en verwarmende soep vol smaak — perfect voor lunch of diner wanneer je zin hebt in iets warms en vullends.
+</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -844,7 +1072,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>vegetarian,gluten-free</t>
+          <t>Ingredients: Water, chicken, beetroot, carrot, onion, sunflower oil, tomato paste, potatoes, white cabbage, cooked beans, salt, garlic, allspice, dill, black pepper, bay leaf.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -852,8 +1080,39 @@
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="40.05" customHeight="1" s="18">
+      <c r="P7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Remove from freezer 5 min before heating. | Pour into a pot and heat on medium for 8–10 minutes, stirring occasionally. | Or microwave in a bowl for 5–7 minutes, stirring halfway. | Serve hot with sour cream and fresh herbs.</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Дістаньте з морозилки за 5 хв до приготування. | Перелийте у каструлю і розігрійте на середньому вогні 8–10 хвилин, час від часу помішуючи. | Або в мікрохвильовці: 5–7 хвилин, помішавши на половині. | Подавати гарячим зі сметаною та свіжою зеленню.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Haal 5 min voor bereiding uit de vriezer. | Giet in een pan en verhit op middelhoog vuur 8–10 min, regelmatig roeren. | Of magnetron: 5–7 min, halverwege roeren. | Serveer heet met zure room en verse kruiden.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Up to 6 months</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>до 6 місяців</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Tot 6 maanden</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64.5" customHeight="1" s="17">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>solyanka</t>
@@ -881,17 +1140,17 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Rich meat soup with olives and lemon. Deep homemade taste, easy to store in the freezer.</t>
+          <t>A rich solyanka made with a variety of meats and sausages. A bold, hearty soup with a slightly tangy taste — a true meat-lover’s classic, perfect when you want something deeply satisfying and warming.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Насичений м'ясний суп з оливками та лимоном. Глибокий домашній смак, легко зберігати.</t>
+          <t>Насичена солянка з різними видами м’яса та ковбасками. Густий, глибокий смак із легкою кислинкою — справжня м’ясна класика, ідеальна, коли хочеться чогось дуже ситного та зігріваючого.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Rijke vleessoep met olijven en citroen. Diepe huisgemaakte smaak, makkelijk in de vriezer.</t>
+          <t>Een rijke solyanka met verschillende soorten vlees en worst. Een krachtige, hartige soep met een lichtzure smaak — een echte klassieker voor vleesliefhebbers, perfect als je zin hebt in iets vullends en verwarmends.</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
@@ -910,7 +1169,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>gluten-free</t>
+          <t>Ingredients: Water, chicken thigh, pork belly (bacon), sausages (beef, pork, chicken), onion, carrot, pickled cucumbers, tomato paste, olives, sunflower oil, salt, garlic, smoked paprika, black pepper.</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -918,8 +1177,39 @@
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="40.05" customHeight="1" s="18">
+      <c r="P8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Remove from freezer 5 min before heating. | Heat in a pot on medium for 8–10 min, stirring occasionally. | Or microwave for 5–7 minutes. | Serve with a slice of lemon and sour cream.</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Дістаньте з морозилки за 5 хв до приготування. | Розігрійте у каструлі на середньому вогні 8–10 хвилин, час від часу помішуючи. | Або в мікрохвильовці 5–7 хвилин. | Подавати з часточкою лимону та сметаною.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Haal 5 min voor bereiding uit de vriezer. | Verhit in een pan op middelhoog vuur 8–10 min, regelmatig roeren. | Of magnetron: 5–7 min. | Serveer met een schijfje citroen en zure room.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Up to 6 months</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>до 6 місяців</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Tot 6 maanden</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="63" customHeight="1" s="17">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>shakshuka</t>
@@ -942,22 +1232,23 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mains</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Spiced tomato base, bold and warming. 1 portion = 2 hearts × 100g. Fry in a pan — done.</t>
+          <t>A flavorful shakshuka base made with tomatoes, peppers, onions, and garlic. We’ve done all the prep — you just need to add the eggs. Perfect for a quick, delicious breakfast or a light dinner.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Гострий томатний соус, яскравий та зігріваючий. 1 порція = 2 серця × 100г.</t>
+          <t xml:space="preserve">Ароматна база для шакшуки з томатів, перцю, цибулі та часнику. Ми вже все підготували — вам залишається лише додати яйця. Ідеальна для швидкого, смачного сніданку або легкої вечері.
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Gekruide tomatenbasis, pittig en verwarmend. 1 portie = 2 hartjes × 100g. Bak in de pan.</t>
+          <t>Een smaakvolle shakshuka basis van tomaten, paprika, ui en knoflook. Wij hebben alles al voorbereid — jij hoeft alleen nog eieren toe te voegen. Perfect voor een snel en lekker ontbijt of een lichte avondmaaltijd.</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -980,7 +1271,8 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>vegetarian,vegan,gluten-free</t>
+          <t xml:space="preserve">Ingredients: Peeled tomatoes, onion, bell pepper, sun-dried tomatoes, sunflower oil, smoked paprika, garlic, ground red pepper.
+</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -989,7 +1281,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.05" customHeight="1" s="18">
+    <row r="10" ht="63" customHeight="1" s="17">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>zrazy</t>
@@ -1017,17 +1309,17 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Pan-fried potato patties with mushroom &amp; cheese filling. Ready in 15 min.</t>
+          <t>Potato zrazy — soft mashed potato patties filled with mushrooms and melted hard cheese. Crispy on the outside, tender and flavorful inside. Perfect for a comforting lunch or dinner.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Картопляні зрази з грибами та сиром. Готові за 15 хв, мінімум посуду.</t>
+          <t>Класичні картопляні зрази з ніжною начинкою з грибів та твердого сиру. Зовні — золотиста скоринка, всередині — м’яка, ароматна текстура. Ідеальні для обіду або вечері, коли хочеться чогось домашнього і ситного.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Gebakken aardappelkoekjes met paddenstoelen en kaas. Klaar in 15 min.</t>
+          <t>Aardappel zrazy — zachte aardappelpasteitjes gevuld met champignons en gesmolten harde kaas. Knapperig van buiten, zacht en vol van smaak van binnen. Perfect voor een warme, vullende maaltijd.</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
@@ -1046,23 +1338,60 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
+          <t>Ingredients: Potatoes, wheat flour (gluten), mushrooms, cheese (milk), fried onion, sunflower oil, salt, black pepper, potato starch.
+Allergens: Contains gluten, milk.</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>vegetarian</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Take zrazy straight from the freezer. | Heat a pan with oil on medium heat. | Fry 5–7 min per side until golden and heated through. | Serve with sour cream or a green salad.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Дістаньте зрази прямо з морозилки. | Розігрійте олію на сковорідці на середньому вогні. | Смажте 5–7 хвилин з кожного боку до золотистого кольору. | Подавати зі сметаною або зеленим салатом.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Haal de zrazy direct uit de vriezer. | Verhit olie in een pan op middelhoog vuur. | Bak 5–7 min per kant tot goudbruin. | Serveer met zure room of een groene salade.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Up to 6 months</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>до 6 місяців</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Tot 6 maanden</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>📦  PRODUCT VARIANTS (sizes &amp; prices)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52.8" customHeight="1" s="18">
+    <row r="13" ht="52.9" customHeight="1" s="17">
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>product_id</t>
@@ -1277,6 +1606,41 @@
         </is>
       </c>
       <c r="F22" s="5" t="n"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>vegetarian</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Remove hearts from packaging while still frozen. | Place in a pan with a little oil on medium heat. | Cover with a lid and heat for 6–8 min until piping hot. | Optionally crack a fresh egg on top for the last 2 min.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Дістаньте серця з упаковки заморозженими. | Покладіть на сковорідку з трохи олією на середньому вогні. | Накрийте кришкою і прогрійте 6–8 хв до гарячого. | За бажанням — розбийте яйце зверху за 2 хвилини до готовності.</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Haal de hartjes bevroren uit de verpakking. | Leg in een pan met een beetje olie op middelhoog vuur. | Dek af en verhit 6–8 min tot goed heet. | Optioneel: breek een vers ei bovenop de laatste 2 minuten.</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Up to 6 months</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>до 6 місяців</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Tot 6 maanden</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
@@ -1329,7 +1693,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1344,35 +1708,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="B1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="4" customWidth="1" style="18" min="2" max="2"/>
-    <col width="20" customWidth="1" style="18" min="3" max="5"/>
-    <col width="10" customWidth="1" style="18" min="6" max="6"/>
-    <col width="45" customWidth="1" style="18" min="7" max="7"/>
-    <col width="12" customWidth="1" style="18" min="8" max="9"/>
-    <col width="25" customWidth="1" style="18" min="10" max="10"/>
-    <col width="15" customWidth="1" style="18" min="11" max="11"/>
-    <col width="8" customWidth="1" style="18" min="12" max="12"/>
+    <col width="4" customWidth="1" style="17" min="2" max="2"/>
+    <col width="20" customWidth="1" style="17" min="3" max="5"/>
+    <col width="10" customWidth="1" style="17" min="6" max="6"/>
+    <col width="45" customWidth="1" style="17" min="7" max="7"/>
+    <col width="12" customWidth="1" style="17" min="8" max="9"/>
+    <col width="25" customWidth="1" style="17" min="10" max="10"/>
+    <col width="15" customWidth="1" style="17" min="11" max="11"/>
+    <col width="8" customWidth="1" style="17" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" s="18">
-      <c r="B1" s="17" t="inlineStr">
+    <row r="1" ht="17.45" customHeight="1" s="17">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>🎁  HUTKO Kitchen — Bundles &amp; Packs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>items = product_id:qty,product_id:qty format. discount_price overrides calculated price.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1" s="18">
+    <row r="4" ht="30" customHeight="1" s="17">
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -1429,7 +1792,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="18">
+    <row r="5" ht="45" customHeight="1" s="17">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>pack-s1</t>
@@ -1437,7 +1800,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Starter Pack — Borscht</t>
+          <t>Starter BOX — Borscht</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1478,7 +1841,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="18">
+    <row r="6" ht="45" customHeight="1" s="17">
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>pack-s2</t>
@@ -1486,7 +1849,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Starter Pack — Solyanka</t>
+          <t>Starter BOX — Solyanka</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1527,7 +1890,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="18">
+    <row r="7" ht="45" customHeight="1" s="17">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>pack-m1</t>
@@ -1535,12 +1898,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Family Pack — Classic</t>
+          <t>Family BOX — Classic</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Сімейний набір — Класик</t>
+          <t>Сімейний набір — Класичний</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1580,7 +1943,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" s="18">
+    <row r="8" ht="45" customHeight="1" s="17">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>pack-m2</t>
@@ -1588,7 +1951,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Family Pack — Solyanka</t>
+          <t>Family BOX  — Solyanka</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1629,7 +1992,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1" s="18">
+    <row r="9" ht="45" customHeight="1" s="17">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>pack-l1</t>
@@ -1637,12 +2000,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Big Pack — Classic</t>
+          <t>Big BOX — Classic</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Великий набір — Класик</t>
+          <t>Великий набір — Класичний</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1678,7 +2041,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" s="18">
+    <row r="10" ht="45" customHeight="1" s="17">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>pack-l2</t>
@@ -1735,7 +2098,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1751,14 +2114,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="75" customWidth="1" style="18" min="1" max="1"/>
-    <col width="25" customWidth="1" style="18" min="2" max="2"/>
-    <col width="60" customWidth="1" style="18" min="3" max="3"/>
+    <col width="75" customWidth="1" style="17" min="1" max="1"/>
+    <col width="25" customWidth="1" style="17" min="2" max="2"/>
+    <col width="60" customWidth="1" style="17" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="18">
+    <row r="1" ht="15.6" customHeight="1" s="17">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>📖  HOW TO USE THIS FILE</t>
@@ -1778,7 +2141,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • photo_file: filename in assets/ folder (also in Images sheet)</t>
+          <t xml:space="preserve">  • photo_file: filename in assets/ folder (also in Images sheet) </t>
         </is>
       </c>
     </row>
@@ -1857,7 +2220,7 @@
     <row r="17">
       <c r="A17" s="8" t="n"/>
     </row>
-    <row r="18" ht="15.6" customHeight="1" s="18">
+    <row r="18" ht="15.6" customHeight="1" s="17">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>⚠️  AFTER EDITING:</t>
@@ -1889,7 +2252,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1906,29 +2269,29 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="12" customWidth="1" style="18" min="1" max="1"/>
-    <col width="16" customWidth="1" style="18" min="2" max="2"/>
-    <col width="24" customWidth="1" style="18" min="3" max="3"/>
-    <col width="55" customWidth="1" style="18" min="4" max="4"/>
+    <col width="12" customWidth="1" style="17" min="1" max="1"/>
+    <col width="16" customWidth="1" style="17" min="2" max="2"/>
+    <col width="24" customWidth="1" style="17" min="3" max="3"/>
+    <col width="55" customWidth="1" style="17" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="18">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="17">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>🖼️  HUTKO Kitchen — Image Manager</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Change photo_file values below to update images on the website. Use relative paths from the frontend folder (e.g. assets/products/syrnyky.png).</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="6" customHeight="1" s="18"/>
+    <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -2223,7 +2586,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2240,28 +2603,28 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="22" customWidth="1" style="18" min="1" max="1"/>
-    <col width="38" customWidth="1" style="18" min="2" max="2"/>
-    <col width="45" customWidth="1" style="18" min="3" max="3"/>
+    <col width="22" customWidth="1" style="17" min="1" max="1"/>
+    <col width="38" customWidth="1" style="17" min="2" max="2"/>
+    <col width="45" customWidth="1" style="17" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="18">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="17">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>⚙️  HUTKO Kitchen — Contact &amp; Business Settings</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Edit values in column B. These are read by the website for the contact page, footer, and delivery info.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="6" customHeight="1" s="18"/>
+    <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2354,7 +2717,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>31600000000</v>
+        <v>31627155200</v>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
@@ -2530,7 +2893,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk_x000d_&amp;1#&amp;"Calibri"&amp;10 &amp;K008000 C0-Openbaar</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri"&amp;10 &amp;KFF0000_x000d_# C2-Vertrouwelijk</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1077,7 +1077,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>assets/products/borscht.png</t>
+          <t>assets/products/borscht.jpeg</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>assets/products/solyanka.png</t>
+          <t>assets/products/solyanka.jpeg</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1341,7 +1341,7 @@
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>assets/products/zrazy.png</t>
+          <t>assets/products/zrazy.jpeg</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1355,11 +1355,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>vegetarian</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Take zrazy straight from the freezer. | Heat a pan with oil on medium heat. | Fry 5–7 min per side until golden and heated through. | Serve with sour cream or a green salad.</t>
@@ -1388,6 +1384,11 @@
       <c r="AD10" t="inlineStr">
         <is>
           <t>Tot 6 maanden</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
         </is>
       </c>
     </row>
@@ -1632,6 +1633,11 @@
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>assets/products/borscht.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
@@ -1653,6 +1659,11 @@
         </is>
       </c>
       <c r="F21" s="6" t="n"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>assets/products/solyanka.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
@@ -1730,6 +1741,17 @@
         </is>
       </c>
       <c r="F23" s="6" t="n"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy.jpeg</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
@@ -1751,6 +1773,17 @@
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy.jpeg</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2444,7 +2477,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>assets/products/borscht.png</t>
+          <t>assets/products/borscht.jpeg</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2499,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>assets/products/solyanka.png</t>
+          <t>assets/products/solyanka.jpeg</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2543,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>assets/products/zrazy.png</t>
+          <t>assets/products/zrazy.jpeg</t>
         </is>
       </c>
     </row>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1107,17 +1107,17 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Up to 6 months</t>
+          <t>Up to 3 months</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>до 6 місяців</t>
+          <t>до 3 місяців</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Tot 6 maanden</t>
+          <t>Tot 3 maanden</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Up to 6 months</t>
+          <t>Up to 3 months</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>до 6 місяців</t>
+          <t>до 3 місяців</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Tot 6 maanden</t>
+          <t>Tot 3 maanden</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>assets/products/shakshuka.png</t>
+          <t>assets/products/shakshuka.jpeg</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1288,6 +1288,26 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>assets/products/shakshuka_2.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="63" customHeight="1" s="17">
       <c r="B10" s="3" t="inlineStr">
@@ -1355,7 +1375,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Take zrazy straight from the freezer. | Heat a pan with oil on medium heat. | Fry 5–7 min per side until golden and heated through. | Serve with sour cream or a green salad.</t>
@@ -1373,17 +1392,17 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Up to 6 months</t>
+          <t>Up to 3 months</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>до 6 місяців</t>
+          <t>до 3 місяців</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Tot 6 maanden</t>
+          <t>Tot 3 maanden</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1638,6 +1657,21 @@
           <t>assets/products/borscht.jpeg</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
@@ -1664,6 +1698,21 @@
           <t>assets/products/solyanka.jpeg</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
@@ -1685,9 +1734,9 @@
         </is>
       </c>
       <c r="F22" s="5" t="n"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>vegetarian</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>assets/products/shakshuka.jpeg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -1707,17 +1756,22 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Up to 6 months</t>
+          <t>Up to 3 months</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>до 6 місяців</t>
+          <t>до 3 місяців</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Tot 6 maanden</t>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>assets/products/shakshuka_2.jpeg</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1800,21 @@
           <t>assets/products/zrazy.jpeg</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
@@ -1778,7 +1846,21 @@
           <t>assets/products/zrazy.jpeg</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Up to 3 months</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>до 3 місяців</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Tot 3 maanden</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
@@ -2521,7 +2603,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>assets/products/shakshuka.png</t>
+          <t>assets/products/shakshuka.jpeg</t>
         </is>
       </c>
     </row>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1533,6 +1533,27 @@
           <t>assets/products/syrnyky.jpeg</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Ingredients: cottage cheese (82.5%), sugar (9.3%), wheat flour (8.2%), vanilla sugar (&lt;0.1%).
+Allergens: milk, gluten (wheat).
+Nutrition per 100g: Energy ~230 kcal · Protein ~15g · Fat ~8g · Carbs ~22g · Sugar ~10g</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Склад: кисломолочний сир (82,5%), цукор (9,3%), пшеничне борошно (8,2%), ванільний цукор (&lt;0,1%).
+Алергени: молоко, глютен (пшениця).
+Поживна цінність на 100г: ~230 ккал · Білки ~15г · Жири ~8г · Вуглеводи ~22г</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Ingrediënten: kwark (82,5%), suiker (9,3%), tarwebloem (8,2%), vanillesuiker (&lt;0,1%).
+Allergenen: melk, gluten (tarwe).
+Voedingswaarden per 100g: ~230 kcal · Eiwit ~15g · Vet ~8g · Koolhydraten ~22g</t>
+        </is>
+      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>assets/products/syrnyky_2.png,assets/products/syrnyky_3.jpeg</t>
@@ -1626,6 +1647,27 @@
           <t>assets/products/chicken.jpeg</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Ingredients: chicken fillet (76%), butter (13%), breadcrumbs (5%), cheese (3.5%), eggs (2.5%), herbs (1%).
+Allergens: milk, eggs, gluten (wheat).
+Nutrition per 100g: Energy ~250 kcal · Protein ~18g · Fat ~17g · Carbs ~6g</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Склад: куряче філе (76%), вершкове масло (13%), панірувальні сухарі (5%), сир (3,5%), яйця (2,5%), зелень (1%).
+Алергени: молоко, яйця, глютен (пшениця).
+Поживна цінність на 100г: ~250 ккал · Білки ~18г · Жири ~17г · Вуглеводи ~6г</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Ingrediënten: kipfilet (76%), boter (13%), paneermeel (5%), kaas (3,5%), eieren (2,5%), kruiden (1%).
+Allergenen: melk, eieren, gluten (tarwe).
+Voedingswaarden per 100g: ~250 kcal · Eiwit ~18g · Vet ~17g · Koolhydraten ~6g</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>assets/products/chicken_2.jpeg,assets/products/chicken_3.jpeg</t>
@@ -1657,6 +1699,27 @@
           <t>assets/products/borscht.jpeg</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ingredients: cabbage (24%), bell pepper (12%), beetroot (12%), meat (12%), potatoes (10%), tomato paste (10%), carrot (5%), onion (3%).
+Allergens: none.
+Nutrition per 100g: Energy ~45 kcal · Protein ~2.5g · Fat ~1.5g · Carbs ~5g</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Склад: капуста (24%), перець (12%), буряк (12%), м'ясо (12%), картопля (10%), томатна паста (10%), морква (5%), цибуля (3%).
+Алергени: відсутні.
+Поживна цінність на 100г: ~45 ккал · Білки ~2,5г · Жири ~1,5г · Вуглеводи ~5г</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Ingrediënten: kool (24%), paprika (12%), biet (12%), vlees (12%), aardappelen (10%), tomatenpuree (10%), wortel (5%), ui (3%).
+Allergenen: geen.
+Voedingswaarden per 100g: ~45 kcal · Eiwit ~2,5g · Vet ~1,5g · Koolhydraten ~5g</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr">
         <is>
           <t>Up to 3 months</t>
@@ -1739,6 +1802,27 @@
           <t>assets/products/shakshuka.jpeg</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Ingredients: bell pepper (42.5%), tomatoes (34%), onion (21%), garlic (2.5%).
+Allergens: none.
+Nutrition per 100g: Energy ~35 kcal · Protein ~1.5g · Fat ~0.3g · Carbs ~7g · Sugar ~5g · Fiber ~2g</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Склад: перець (42,5%), томати (34%), цибуля (21%), часник (2,5%).
+Алергени: відсутні.
+Поживна цінність на 100г: ~35 ккал · Білки ~1,5г · Жири ~0,3г · Вуглеводи ~7г</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Ingrediënten: paprika (42,5%), tomaten (34%), ui (21%), knoflook (2,5%).
+Allergenen: geen.
+Voedingswaarden per 100g: ~35 kcal · Eiwit ~1,5g · Vet ~0,3g · Koolhydraten ~7g</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>Remove hearts from packaging while still frozen. | Place in a pan with a little oil on medium heat. | Cover with a lid and heat for 6–8 min until piping hot. | Optionally crack a fresh egg on top for the last 2 min.</t>
@@ -1844,6 +1928,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>assets/products/zrazy.jpeg</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Ingredients: potatoes (55%), mushrooms (28%), wheat flour (10%), cheese (7%), eggs (5%).
+Allergens: milk, eggs, gluten (wheat).
+Nutrition per 100g: Energy ~140 kcal · Protein ~4g · Fat ~3g · Carbs ~24g</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Склад: картопля (55%), гриби (28%), пшеничне борошно (10%), сир (7%), яйця (5%).
+Алергени: молоко, яйця, глютен (пшениця).
+Поживна цінність на 100г: ~140 ккал · Білки ~4г · Жири ~3г · Вуглеводи ~24г</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Ingrediënten: aardappelen (55%), champignons (28%), tarwebloem (10%), kaas (7%), eieren (5%).
+Allergenen: melk, eieren, gluten (tarwe).
+Voedingswaarden per 100g: ~140 kcal · Eiwit ~4g · Vet ~3g · Koolhydraten ~24g</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +242,7 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -607,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF24"/>
+  <dimension ref="B1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="4" customWidth="1" style="17" min="2" max="2"/>
@@ -634,7 +635,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="17">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -1411,7 +1411,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="19" t="inlineStr">
         <is>
@@ -1996,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L10"/>
+  <dimension ref="B1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="4" customWidth="1" style="17" min="2" max="2"/>
@@ -2079,6 +2078,21 @@
           <t>active</t>
         </is>
       </c>
+      <c r="M4" s="29" t="inlineStr">
+        <is>
+          <t>choice_en</t>
+        </is>
+      </c>
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t>choice_ua</t>
+        </is>
+      </c>
+      <c r="O4" s="29" t="inlineStr">
+        <is>
+          <t>choice_nl</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="17">
       <c r="B5" s="2" t="inlineStr">
@@ -2128,6 +2142,21 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Zrazy 6 pcs  OR  Chicken balls 8 pcs</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Зрази 6 шт  АБО  Курячі кульки 8 шт</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Zrazy 6 st  OF  Kippenballen 8 st</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1" s="17">
       <c r="B6" s="3" t="inlineStr">
@@ -2177,6 +2206,21 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Zrazy 6 pcs  OR  Chicken balls 8 pcs</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Зрази 6 шт  АБО  Курячі кульки 8 шт</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Zrazy 6 st  OF  Kippenballen 8 st</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1" s="17">
       <c r="B7" s="2" t="inlineStr">
@@ -2230,6 +2274,21 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Zrazy 12 pcs  OR  Chicken balls 16 pcs</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Зрази 12 шт  АБО  Курячі кульки 16 шт</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Zrazy 12 st  OF  Kippenballen 16 st</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1" s="17">
       <c r="B8" s="3" t="inlineStr">
@@ -2279,6 +2338,21 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Zrazy 12 pcs  OR  Chicken balls 16 pcs</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Зрази 12 шт  АБО  Курячі кульки 16 шт</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Zrazy 12 st  OF  Kippenballen 16 st</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1" s="17">
       <c r="B9" s="2" t="inlineStr">
@@ -2328,6 +2402,21 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Zrazy 16 pcs  OR  Chicken balls 20 pcs</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Зрази 16 шт  АБО  Курячі кульки 20 шт</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Zrazy 16 st  OF  Kippenballen 20 st</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1" s="17">
       <c r="B10" s="3" t="inlineStr">
@@ -2375,6 +2464,21 @@
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Zrazy 16 pcs  OR  Chicken balls 20 pcs</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Зрази 16 шт  АБО  Курячі кульки 20 шт</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Zrazy 16 st  OF  Kippenballen 20 st</t>
         </is>
       </c>
     </row>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1995,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="4" customWidth="1" style="17" min="2" max="2"/>
@@ -2022,6 +2022,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="17">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -2097,46 +2098,46 @@
     <row r="5" ht="45" customHeight="1" s="17">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>pack-s1</t>
+          <t>pack-m1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Starter BOX — Borscht</t>
+          <t>Pack M (1) — Syrnyky + Borscht</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Стартовий набір — Борщ</t>
+          <t>Набір M (1) — Сирники + Борщ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Starterpakket — Borsjt</t>
+          <t>Pack M (1) — Syrnyky + Borsjt</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Pack S</t>
+          <t>Pack M</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>syrnyky:8,borscht:1,zrazy:6,chicken:8</t>
+          <t>syrnyky:16,borscht:2</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>assets/Bundles/s_pack_orange.png</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n"/>
+          <t>assets/Bundles/packM_72euro.PNG</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2144,63 +2145,67 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Zrazy 6 pcs  OR  Chicken balls 8 pcs</t>
+          <t>Zrazy 12 pcs OR Chicken balls 16 pcs OR Mlyntsi 12 pcs</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Зрази 6 шт  АБО  Курячі кульки 8 шт</t>
+          <t>Зрази 12 шт АБО Курячі кульки 16 шт АБО Млинці 12 шт</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Zrazy 6 st  OF  Kippenballen 8 st</t>
+          <t>Zrazy 12 st OF Chicken balls 16 st OF Mlyntsi 12 st</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" s="17">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>pack-s2</t>
+          <t>pack-m2</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Starter BOX — Solyanka</t>
+          <t>Pack M (2) — Syrnyky + Shakshuka + Solyanka</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стартовий набір — Солянка</t>
+          <t>Набір M (2) — Сирники + Шакшука + Солянка</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Starterpakket — Solyanka</t>
+          <t>Pack M (2) — Syrnyky + Shakshuka + Solyanka</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Pack S</t>
+          <t>Pack M</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>syrnyky:8,solyanka:1,zrazy:6,chicken:8</t>
+          <t>syrnyky:8,shakshuka:2,solyanka:2</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>assets/Bundles/s_pack_blue.jpeg</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n"/>
+          <t>assets/Bundles/packM_80euro.JPEG</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Most popular</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2208,67 +2213,63 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Zrazy 6 pcs  OR  Chicken balls 8 pcs</t>
+          <t>Zrazy 12 pcs OR Chicken balls 16 pcs OR Mlyntsi 12 pcs</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Зрази 6 шт  АБО  Курячі кульки 8 шт</t>
+          <t>Зрази 12 шт АБО Курячі кульки 16 шт АБО Млинці 12 шт</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Zrazy 6 st  OF  Kippenballen 8 st</t>
+          <t>Zrazy 12 st OF Chicken balls 16 st OF Mlyntsi 12 st</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" s="17">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>pack-m1</t>
+          <t>pack-l1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Family BOX — Classic</t>
+          <t>Pack L (1) — Syrnyky + Borscht + Solyanka</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Сімейний набір — Класичний</t>
+          <t>Набір L (1) — Сирники + Борщ + Солянка</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Familiepakket — Klassiek</t>
+          <t>Pack L (1) — Syrnyky + Borsjt + Solyanka</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pack M</t>
+          <t>Pack L</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>syrnyky:16,borscht:2,zrazy:12,chicken:16</t>
+          <t>syrnyky:24,borscht:2,solyanka:1</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>assets/Bundles/m_pack_orange.png</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Most popular</t>
-        </is>
-      </c>
+          <t>assets/Bundles/packL_95euro.PNG</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2276,63 +2277,63 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Zrazy 12 pcs  OR  Chicken balls 16 pcs</t>
+          <t>Zrazy 12 pcs OR Chicken balls 16 pcs OR Mlyntsi 12 pcs</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Зрази 12 шт  АБО  Курячі кульки 16 шт</t>
+          <t>Зрази 12 шт АБО Курячі кульки 16 шт АБО Млинці 12 шт</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Zrazy 12 st  OF  Kippenballen 16 st</t>
+          <t>Zrazy 12 st OF Chicken balls 16 st OF Mlyntsi 12 st</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" s="17">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>pack-m2</t>
+          <t>pack-l2</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Family BOX  — Solyanka</t>
+          <t>Pack L (2) — Syrnyky + Borscht + Solyanka + Shakshuka</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Сімейний набір — Солянка</t>
+          <t>Набір L (2) — Сирники + Борщ + Солянка + Шакшука</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Familiepakket — Solyanka</t>
+          <t>Pack L (2) — Syrnyky + Borsjt + Solyanka + Shakshuka</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Pack M</t>
+          <t>Pack L</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>syrnyky:8,shakshuka:2,solyanka:2,zrazy:12,chicken:16</t>
+          <t>syrnyky:16,borscht:1,solyanka:2,shakshuka:2</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>assets/Bundles/m_pack_blue.png</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
+          <t>assets/Bundles/packL_100euro.PNG</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2340,147 +2341,45 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Zrazy 12 pcs  OR  Chicken balls 16 pcs</t>
+          <t>Zrazy 12 pcs OR Chicken balls 16 pcs OR Mlyntsi 12 pcs</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Зрази 12 шт  АБО  Курячі кульки 16 шт</t>
+          <t>Зрази 12 шт АБО Курячі кульки 16 шт АБО Млинці 12 шт</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Zrazy 12 st  OF  Kippenballen 16 st</t>
+          <t>Zrazy 12 st OF Chicken balls 16 st OF Mlyntsi 12 st</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1" s="17">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>pack-l1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Big BOX — Classic</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Великий набір — Класичний</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Groot pakket — Klassiek</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Pack L</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>syrnyky:24,borscht:2,solyanka:1,zrazy:16,chicken:20</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>assets/Bundles/l_pack_blue.png</t>
-        </is>
-      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Zrazy 16 pcs  OR  Chicken balls 20 pcs</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Зрази 16 шт  АБО  Курячі кульки 20 шт</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Zrazy 16 st  OF  Kippenballen 20 st</t>
-        </is>
-      </c>
+      <c r="L9" s="2" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1" s="17">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>pack-l2</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Big Pack — Solyanka</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Великий набір — Солянка</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Groot pakket — Solyanka</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Pack L</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>syrnyky:16,shakshuka:2,borscht:1,solyanka:2,zrazy:16,chicken:20</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>assets/Bundles/l_pack_orange.jpeg</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Zrazy 16 pcs  OR  Chicken balls 20 pcs</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Зрази 16 шт  АБО  Курячі кульки 20 шт</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Zrazy 16 st  OF  Kippenballen 20 st</t>
-        </is>
-      </c>
+      <c r="L10" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -1995,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="B1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="4" customWidth="1" style="17" min="2" max="2"/>
@@ -2022,7 +2022,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="17">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -2799,7 +2798,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/m_pack_orange.png</t>
+          <t>assets/Bundles/packM_72euro.PNG</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2820,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/m_pack_blue.png</t>
+          <t>assets/Bundles/packM_80euro.JPEG</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2842,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/l_pack_blue.png</t>
+          <t>assets/Bundles/packL_95euro.PNG</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2864,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/l_pack_orange.jpeg</t>
+          <t>assets/Bundles/packL_100euro.PNG</t>
         </is>
       </c>
     </row>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vincienergies-my.sharepoint.com/personal/nastia_polimasheva_vinci-energies_net/Documents/Documenten/Documents/Hutko/HUTKO-kitchen/backend/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nastia.polimasheva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_92ABC2B077A49FC32D463E50D597732D6658C472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CEE484A-6782-48E8-9E1E-3C6B6280D4AE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD575ED-63C0-44E3-B3F1-941E7EAEAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="286">
   <si>
     <t>🛒  HUTKO Kitchen — Product Catalogue</t>
   </si>
@@ -422,6 +422,9 @@
     <t>assets/products/julien_balls.PNG</t>
   </si>
   <si>
+    <t>assets/products/julien_balls_2.PNG</t>
+  </si>
+  <si>
     <t>mlyntsi</t>
   </si>
   <si>
@@ -434,13 +437,13 @@
     <t>Mlyntsi (Crêpes)</t>
   </si>
   <si>
-    <t>Thin Ukrainian crêpes — available with chicken &amp; mushroom or cottage cheese filling</t>
+    <t>Thin Ukrainian crêpes — chicken &amp; mushroom or cottage cheese filling</t>
   </si>
   <si>
     <t>Тонкі українські млинці — з начинкою курка &amp; гриби або сир</t>
   </si>
   <si>
-    <t>Dunne Oekraïense pannenkoekjes — met kip &amp; champignon of kwark vulling</t>
+    <t>Dunne Oekraïense pannenkoekjes — kip &amp; champignon of kwark vulling</t>
   </si>
   <si>
     <t>assets/products/mlyntsi.PNG</t>
@@ -555,9 +558,6 @@
     <t>Ingrediënten: aardappelen (55%), champignons (28%), tarwebloem (10%), kaas (7%), eieren (5%).
 Allergenen: melk, eieren, gluten (tarwe).
 Voedingswaarden per 100g: ~140 kcal · Eiwit ~4g · Vet ~3g · Koolhydraten ~24g</t>
-  </si>
-  <si>
-    <t>Chicken &amp; mushrooms 6 pcs</t>
   </si>
   <si>
     <t>Cottage cheese 6 pcs</t>
@@ -1452,10 +1452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AE30"/>
+  <dimension ref="B1:AE31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="4" style="16" customWidth="1"/>
     <col min="3" max="5" width="18" style="16" customWidth="1"/>
     <col min="6" max="6" width="12" style="16" customWidth="1"/>
     <col min="7" max="9" width="40" style="16" customWidth="1"/>
@@ -2012,35 +2012,37 @@
       <c r="M11" t="s">
         <v>129</v>
       </c>
-      <c r="N11"/>
       <c r="O11" t="s">
         <v>43</v>
       </c>
+      <c r="AE11" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F12" t="s">
         <v>123</v>
       </c>
       <c r="G12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J12">
         <v>14</v>
@@ -2052,80 +2054,36 @@
         <v>128</v>
       </c>
       <c r="M12" t="s">
-        <v>137</v>
-      </c>
-      <c r="N12"/>
+        <v>138</v>
+      </c>
       <c r="O12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:31" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="2:31" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B14" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-    </row>
-    <row r="15" spans="2:31" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+    </row>
+    <row r="17" spans="2:31" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="5">
-        <v>13</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="M16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="D17" s="6">
-        <v>23</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="M17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.3">
@@ -2133,10 +2091,10 @@
         <v>32</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="D18" s="5">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>43</v>
@@ -2145,59 +2103,59 @@
       <c r="M18" t="s">
         <v>41</v>
       </c>
-      <c r="N18" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>145</v>
-      </c>
-      <c r="R18" t="s">
-        <v>146</v>
-      </c>
       <c r="AE18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="D19" s="6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="6"/>
       <c r="M19" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="AE19" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D20" s="5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="5"/>
       <c r="M20" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="N20" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>146</v>
+      </c>
+      <c r="R20" t="s">
+        <v>147</v>
       </c>
       <c r="AE20" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.3">
@@ -2205,10 +2163,10 @@
         <v>55</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="D21" s="6">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>43</v>
@@ -2217,116 +2175,86 @@
       <c r="M21" t="s">
         <v>62</v>
       </c>
-      <c r="N21" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>149</v>
-      </c>
-      <c r="R21" t="s">
-        <v>150</v>
-      </c>
       <c r="AE21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="D22" s="5">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F22" s="5"/>
       <c r="M22" t="s">
-        <v>78</v>
-      </c>
-      <c r="N22" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>152</v>
-      </c>
-      <c r="R22" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="D23" s="6">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="6"/>
       <c r="M23" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="N23" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>150</v>
+      </c>
+      <c r="R23" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B24" s="5" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="D24" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F24" s="5"/>
       <c r="M24" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="N24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="R24" t="s">
-        <v>157</v>
-      </c>
-      <c r="V24" t="s">
-        <v>158</v>
-      </c>
-      <c r="W24" t="s">
-        <v>159</v>
-      </c>
-      <c r="X24" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="AB24" t="s">
         <v>51</v>
@@ -2337,26 +2265,23 @@
       <c r="AD24" t="s">
         <v>53</v>
       </c>
-      <c r="AE24" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D25" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="6"/>
       <c r="M25" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="AB25" t="s">
         <v>51</v>
@@ -2367,35 +2292,41 @@
       <c r="AD25" t="s">
         <v>53</v>
       </c>
-      <c r="AE25" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="26" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D26" s="5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F26" s="5"/>
       <c r="M26" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="N26" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="Q26" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="R26" t="s">
-        <v>164</v>
+        <v>158</v>
+      </c>
+      <c r="V26" t="s">
+        <v>159</v>
+      </c>
+      <c r="W26" t="s">
+        <v>160</v>
+      </c>
+      <c r="X26" t="s">
+        <v>161</v>
       </c>
       <c r="AB26" t="s">
         <v>51</v>
@@ -2407,43 +2338,84 @@
         <v>53</v>
       </c>
       <c r="AE26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B27" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="6">
+        <v>15</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="M27" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
+    <row r="28" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B28" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="5">
+        <v>28</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="28" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28">
-        <v>21</v>
-      </c>
-      <c r="E28" t="s">
-        <v>43</v>
+      <c r="F28" s="5"/>
+      <c r="M28" t="s">
+        <v>112</v>
+      </c>
+      <c r="N28" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>164</v>
+      </c>
+      <c r="R28" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D29">
         <v>15</v>
@@ -2454,15 +2426,29 @@
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30">
+        <v>21</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
         <v>166</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>14</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2928,7 +2914,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>13</v>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nastia.polimasheva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vincienergies-my.sharepoint.com/personal/nastia_polimasheva_vinci-energies_net/Documents/Documenten/Documents/Hutko/HUTKO-kitchen/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD575ED-63C0-44E3-B3F1-941E7EAEAB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/backend/hutko_shop.xlsx
+++ b/backend/hutko_shop.xlsx
@@ -217,7 +217,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -240,6 +239,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE32"/>
+  <dimension ref="B1:AE32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="26" min="2" max="2"/>
@@ -638,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="26">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -700,7 +699,7 @@
           <t>photo_file</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t>ingredients_en</t>
         </is>
@@ -710,82 +709,82 @@
           <t>active</t>
         </is>
       </c>
-      <c r="P4" s="18" t="inlineStr">
+      <c r="P4" s="17" t="inlineStr">
         <is>
           <t>dietary</t>
         </is>
       </c>
-      <c r="Q4" s="19" t="inlineStr">
+      <c r="Q4" s="18" t="inlineStr">
         <is>
           <t>ingredients_ua</t>
         </is>
       </c>
-      <c r="R4" s="19" t="inlineStr">
+      <c r="R4" s="18" t="inlineStr">
         <is>
           <t>ingredients_nl</t>
         </is>
       </c>
-      <c r="S4" s="20" t="inlineStr">
+      <c r="S4" s="19" t="inlineStr">
         <is>
           <t>about_en</t>
         </is>
       </c>
-      <c r="T4" s="20" t="inlineStr">
+      <c r="T4" s="19" t="inlineStr">
         <is>
           <t>about_ua</t>
         </is>
       </c>
-      <c r="U4" s="20" t="inlineStr">
+      <c r="U4" s="19" t="inlineStr">
         <is>
           <t>about_nl</t>
         </is>
       </c>
-      <c r="V4" s="21" t="inlineStr">
+      <c r="V4" s="20" t="inlineStr">
         <is>
           <t>prepare_en</t>
         </is>
       </c>
-      <c r="W4" s="21" t="inlineStr">
+      <c r="W4" s="20" t="inlineStr">
         <is>
           <t>prepare_ua</t>
         </is>
       </c>
-      <c r="X4" s="21" t="inlineStr">
+      <c r="X4" s="20" t="inlineStr">
         <is>
           <t>prepare_nl</t>
         </is>
       </c>
-      <c r="Y4" s="22" t="inlineStr">
+      <c r="Y4" s="21" t="inlineStr">
         <is>
           <t>hutko_tip_en</t>
         </is>
       </c>
-      <c r="Z4" s="22" t="inlineStr">
+      <c r="Z4" s="21" t="inlineStr">
         <is>
           <t>hutko_tip_ua</t>
         </is>
       </c>
-      <c r="AA4" s="22" t="inlineStr">
+      <c r="AA4" s="21" t="inlineStr">
         <is>
           <t>hutko_tip_nl</t>
         </is>
       </c>
-      <c r="AB4" s="23" t="inlineStr">
+      <c r="AB4" s="22" t="inlineStr">
         <is>
           <t>storage_en</t>
         </is>
       </c>
-      <c r="AC4" s="23" t="inlineStr">
+      <c r="AC4" s="22" t="inlineStr">
         <is>
           <t>storage_ua</t>
         </is>
       </c>
-      <c r="AD4" s="23" t="inlineStr">
+      <c r="AD4" s="22" t="inlineStr">
         <is>
           <t>storage_nl</t>
         </is>
       </c>
-      <c r="AE4" s="23" t="inlineStr">
+      <c r="AE4" s="22" t="inlineStr">
         <is>
           <t>gallery</t>
         </is>
@@ -1416,65 +1415,66 @@
       </c>
     </row>
     <row r="11" ht="52.95" customHeight="1" s="26">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>julien_balls</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Julien Kyiv Meat Balls</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Котлети Жульєн по-Київськи</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Julienne Kyiv Gehaktballen</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>mains</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Golden crispy chicken balls filled with creamy mushroom &amp; cheese julienne</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Золотисті хрусткі курячі кульки з кремовим жульєном з грибів та сиру</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Gouden knapperige kipballen gevuld met romelijke champignon &amp; kaas julienne</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>4 pcs</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>assets/products/julien_balls.png</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1485,72 +1485,72 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
+    <row r="12" ht="22.8" customHeight="1" s="26">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>mlyntsi</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Mlyntsi</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Млинці</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Mlyntsi (Crêpes)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>mains</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Thin Ukrainian crêpes — chicken &amp; mushroom or cottage cheese filling</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Тонкі українські млинці — з начинкою курка &amp; гриби або сир</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Dunne Oekraïense pannenkoekjes — kip &amp; champignon of kwark vulling</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>6 pcs</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>assets/products/mlyntsi.png</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" s="28" t="inlineStr">
         <is>
@@ -1558,8 +1558,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17" ht="52.8" customHeight="1" s="26">
       <c r="B17" s="4" t="inlineStr">
         <is>
@@ -2114,84 +2112,88 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>julien_balls</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>4 pcs</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>julien_balls</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>6 pcs</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>mlyntsi</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Cottage cheese 6 pcs</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>mlyntsi</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Chicken &amp; mushrooms 6 pcs</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F32" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2217,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="B1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="26" min="2" max="2"/>
@@ -2244,7 +2246,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="26">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -2301,17 +2302,17 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M4" s="24" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t>choice_en</t>
         </is>
       </c>
-      <c r="N4" s="24" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t>choice_ua</t>
         </is>
       </c>
-      <c r="O4" s="24" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t>choice_nl</t>
         </is>
@@ -2781,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="26" min="1" max="1"/>
@@ -2862,7 +2863,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyiv Chicken Balls</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -2962,44 +2963,44 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>bundle</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pack-s1</t>
+          <t>julien_balls</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Starter Pack S</t>
+          <t>Julien_Balls</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/s_pack_orange.png</t>
+          <t>assets/products/julien_balls.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>bundle</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pack-s2</t>
+          <t>mlyntsi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Starter Pack S (2)</t>
+          <t>Mlyntsi</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/s_pack_blue.jpeg</t>
+          <t>assets/products/mlyntsi.png</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3017,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Family Pack M</t>
+          <t>Pack_M1</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/m_pack_orange.png</t>
+          <t>assets/Bundles/packM_72euro.png</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3039,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Family Pack M (2)</t>
+          <t>Pack_M2</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/m_pack_blue.png</t>
+          <t>assets/Bundles/packM_80euro.jpeg</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3061,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Big Pack L</t>
+          <t>Pack_L1</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/l_pack_blue.png</t>
+          <t>assets/Bundles/packL_95euro.png</t>
         </is>
       </c>
     </row>
@@ -3082,15 +3083,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Big Pack L (2)</t>
+          <t>Pack_L2</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>assets/Bundles/l_pack_orange.jpeg</t>
-        </is>
-      </c>
-    </row>
+          <t>assets/Bundles/packL_100euro.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
